--- a/events/Pietermaritzburg_2017_MAR/Pietermaritzburg_2017_MAR_Results.xlsx
+++ b/events/Pietermaritzburg_2017_MAR/Pietermaritzburg_2017_MAR_Results.xlsx
@@ -1207,6 +1207,11 @@
           <t>01:42:37.780</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>71555</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3054,6 +3059,11 @@
           <t>01:47:25.590</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>76943</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6362,6 +6372,11 @@
           <t>01:38:03.490</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>72613</t>
+        </is>
+      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>72612</t>
@@ -6994,6 +7009,11 @@
       <c r="L97" t="n">
         <v>525</v>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>76507</t>
+        </is>
+      </c>
       <c r="S97" t="inlineStr">
         <is>
           <t>80679</t>
@@ -7209,6 +7229,11 @@
           <t>70457</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>79174</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7744,6 +7769,11 @@
           <t>01:54:14.340</t>
         </is>
       </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11161,6 +11191,11 @@
           <t>02:16:42.460</t>
         </is>
       </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11931,6 +11966,11 @@
           <t>02:09:37.910</t>
         </is>
       </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>48400</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12060,6 +12100,11 @@
           <t>02:09:39.410</t>
         </is>
       </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -13524,6 +13569,11 @@
       <c r="N196" t="n">
         <v>25</v>
       </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>82195</t>
+        </is>
+      </c>
       <c r="X196" t="inlineStr">
         <is>
           <t>LAP</t>
@@ -15454,6 +15504,11 @@
           <t>02:09:47.950</t>
         </is>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>71569</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -15792,6 +15847,11 @@
           <t>02:00:10.150</t>
         </is>
       </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>48400</t>
+        </is>
+      </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>58216</t>
@@ -15859,6 +15919,11 @@
           <t>02:00:11.460</t>
         </is>
       </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>49664</t>
@@ -16971,6 +17036,11 @@
       </c>
       <c r="L246" t="n">
         <v>611</v>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -17060,7 +17130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21969,6 +22039,204 @@
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>48400</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Hank</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>MCGREGOR</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Mads Brandt</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>PEDERSEN</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>BOROS</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>BARROS</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>71555</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Rita</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>FERNANDES</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>72613</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>76943</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Yaroslov Oleg</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>SHELESTENKO OCUNEVA</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>79174</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>DUBOIS DUNILAC</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>82195</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Philip</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>PIRIE</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Pietermaritzburg_2017_MAR/Pietermaritzburg_2017_MAR_Results.xlsx
+++ b/events/Pietermaritzburg_2017_MAR/Pietermaritzburg_2017_MAR_Results.xlsx
@@ -4941,6 +4941,11 @@
           <t>01:35:13.250</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>65695</t>
+        </is>
+      </c>
       <c r="S67" t="inlineStr">
         <is>
           <t>79147</t>
@@ -7970,6 +7975,11 @@
           <t>01:56:32.490</t>
         </is>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>94098</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9946,6 +9956,11 @@
           <t>02:08:13.410</t>
         </is>
       </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -15994,6 +16009,11 @@
       <c r="R231" t="inlineStr">
         <is>
           <t>48405</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>94098</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D232"/>
+  <dimension ref="A1:D235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22237,6 +22257,72 @@
         </is>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>65695</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Anne Hauge</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SØRENSEN</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>94098</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Jean</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>VAN DER WESTHUIZEN</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Kristina</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>BEDEC</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
